--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484267_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484267_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.164099999999999</v>
+        <v>8.9056</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6281</v>
+        <v>5.5876</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5359</v>
+        <v>3.318</v>
       </c>
       <c r="G2" t="n">
         <v>8.1181</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6553</v>
+        <v>0.3968</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1594</v>
+        <v>-0.2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8148</v>
+        <v>0.5969</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1138</v>
+        <v>7.2908</v>
       </c>
       <c r="E3" t="n">
-        <v>3.063</v>
+        <v>3.7302</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0508</v>
+        <v>3.5606</v>
       </c>
       <c r="G3" t="n">
         <v>0.6071</v>
@@ -688,13 +688,13 @@
         <v>3.3208</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5067</v>
+        <v>0.6837</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6382</v>
+        <v>0.029</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1449</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>3.6559</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.557</v>
+        <v>4.1447</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7412</v>
+        <v>3.4379</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8158</v>
+        <v>0.7068</v>
       </c>
       <c r="G4" t="n">
         <v>2.0083</v>
@@ -766,13 +766,13 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4901</v>
+        <v>1.0778</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0594</v>
+        <v>0.756</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4308</v>
+        <v>0.3218</v>
       </c>
       <c r="V4" t="n">
         <v>0.2772</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5968</v>
+        <v>3.1833</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3227</v>
+        <v>3.7865</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2742</v>
+        <v>-0.6032</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7831</v>
+        <v>0.9635</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0668</v>
+        <v>0.396</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2837</v>
+        <v>0.5675</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0912</v>
+        <v>2.3366</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9698</v>
+        <v>1.2292</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1214</v>
+        <v>1.1074</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3081</v>
+        <v>-1.3731</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.903</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4051</v>
+        <v>-0.5399</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6965</v>
+        <v>0.5668</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2631</v>
+        <v>0.2312</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4335</v>
+        <v>0.3356</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0549</v>
+        <v>-0.8865</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0549</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7959</v>
+        <v>2.4616</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7259</v>
+        <v>1.4326</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.93</v>
+        <v>1.029</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9635</v>
+        <v>0.7831</v>
       </c>
       <c r="H6" t="n">
-        <v>0.396</v>
+        <v>1.0668</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5675</v>
+        <v>-0.2837</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3366</v>
+        <v>2.0912</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2292</v>
+        <v>1.9698</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1074</v>
+        <v>0.1214</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3731</v>
+        <v>-1.3081</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-0.903</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5399</v>
+        <v>-0.4051</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="Q6" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5613</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.1883</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.5395</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1795</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.1707</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.008800000000000001</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.8865</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.2186</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-2.1052</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2822</v>
+        <v>2.2689</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6736</v>
+        <v>1.633</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6086</v>
+        <v>0.6358</v>
       </c>
       <c r="G7" t="n">
         <v>2.7479</v>
@@ -1000,13 +1000,13 @@
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2135</v>
+        <v>0.2001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0689</v>
+        <v>0.0283</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1446</v>
+        <v>0.1719</v>
       </c>
       <c r="V7" t="n">
         <v>-2.4373</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6811</v>
+        <v>0.8761</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5536</v>
+        <v>-0.3314</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2347</v>
+        <v>1.2075</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0045</v>
@@ -1078,13 +1078,13 @@
         <v>2.5395</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4001</v>
+        <v>0.595</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1457</v>
+        <v>0.0765</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5457</v>
+        <v>0.5185</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2772</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1037</v>
+        <v>0.3903</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3186</v>
+        <v>-2.0153</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2149</v>
+        <v>2.4056</v>
       </c>
       <c r="G9" t="n">
         <v>1.7832</v>
@@ -1156,13 +1156,13 @@
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5195</v>
+        <v>-0.0255</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1678</v>
+        <v>0.1356</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3517</v>
+        <v>-0.161</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8336</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5582</v>
+        <v>2.356</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3919</v>
+        <v>-3.3374</v>
       </c>
       <c r="G10" t="n">
         <v>1.391</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4545</v>
+        <v>0.3068</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5531</v>
+        <v>0.3508</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0985</v>
+        <v>-0.044</v>
       </c>
       <c r="V10" t="n">
         <v>-3.6559</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2264</v>
+        <v>-2.3801</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9977</v>
+        <v>-4.5327</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7713</v>
+        <v>2.1526</v>
       </c>
       <c r="G11" t="n">
         <v>-0.5685</v>
@@ -1312,13 +1312,13 @@
         <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8764999999999999</v>
+        <v>-0.0303</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7125</v>
+        <v>-0.2475</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.164</v>
+        <v>0.2173</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6093</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7683</v>
+        <v>-3.2955</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3196</v>
+        <v>-1.9558</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4486</v>
+        <v>-1.3397</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1753</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1557</v>
+        <v>0.3171</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0935</v>
+        <v>0.2704</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0622</v>
+        <v>0.0467</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2186</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.2589</v>
+        <v>22.8643</v>
       </c>
       <c r="E13" t="n">
-        <v>12.5232</v>
+        <v>13.1286</v>
       </c>
       <c r="F13" t="n">
-        <v>9.7357</v>
+        <v>9.7356</v>
       </c>
       <c r="G13" t="n">
         <v>13.6539</v>
@@ -1468,13 +1468,13 @@
         <v>21.4878</v>
       </c>
       <c r="S13" t="n">
-        <v>4.044499999999999</v>
+        <v>4.6496</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1981</v>
+        <v>1.8032</v>
       </c>
       <c r="U13" t="n">
-        <v>2.8467</v>
+        <v>2.846699999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-5.2066</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2353</v>
+        <v>2.2146</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7582</v>
+        <v>1.6571</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4771</v>
+        <v>0.5574</v>
       </c>
       <c r="G14" t="n">
         <v>-2.1933</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4287</v>
+        <v>0.4079</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2037</v>
+        <v>0.1026</v>
       </c>
       <c r="U14" t="n">
-        <v>0.225</v>
+        <v>0.3053</v>
       </c>
       <c r="V14" t="n">
         <v>2.4373</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2568</v>
+        <v>0.4174</v>
       </c>
       <c r="E15" t="n">
         <v>2.4025</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.1458</v>
+        <v>-1.9851</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0398</v>
@@ -1624,13 +1624,13 @@
         <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0814</v>
+        <v>0.2421</v>
       </c>
       <c r="T15" t="n">
         <v>-0.0989</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1803</v>
+        <v>0.341</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1522</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7088</v>
+        <v>0.0392</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4646</v>
+        <v>0.9702</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1734</v>
+        <v>-0.931</v>
       </c>
       <c r="G16" t="n">
         <v>-4.9324</v>
@@ -1702,13 +1702,13 @@
         <v>1.9534</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5107</v>
+        <v>0.2373</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8803</v>
+        <v>-0.3747</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3696</v>
+        <v>0.612</v>
       </c>
       <c r="V16" t="n">
         <v>2.7809</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8635</v>
+        <v>-0.4747</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.537</v>
+        <v>-0.3348</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3265</v>
+        <v>-0.1399</v>
       </c>
       <c r="G17" t="n">
         <v>1.1225</v>
@@ -1780,13 +1780,13 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8139</v>
+        <v>-0.4251</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5915</v>
+        <v>-0.3892</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2225</v>
+        <v>-0.0359</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1495</v>
+        <v>-1.872</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5698</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5796</v>
+        <v>-1.2011</v>
       </c>
       <c r="G18" t="n">
         <v>0.5086000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9646</v>
+        <v>-0.6871</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3548</v>
+        <v>-0.4559</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6098</v>
+        <v>-0.2312</v>
       </c>
       <c r="V18" t="n">
         <v>1.0413</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4715</v>
+        <v>-2.5246</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2006</v>
+        <v>-1.6051</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2709</v>
+        <v>-0.9195</v>
       </c>
       <c r="G19" t="n">
         <v>2.0545</v>
@@ -1936,13 +1936,13 @@
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5316</v>
+        <v>-0.5847</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.341</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1905</v>
+        <v>0.1608</v>
       </c>
       <c r="V19" t="n">
         <v>0.4984</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0564</v>
+        <v>-3.9488</v>
       </c>
       <c r="E20" t="n">
         <v>-3.1864</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.87</v>
+        <v>-0.7624</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5403</v>
@@ -2014,13 +2014,13 @@
         <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7528</v>
+        <v>-0.6452</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2283</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5245</v>
+        <v>-0.4169</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1773</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6225</v>
+        <v>-4.2565</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8586</v>
+        <v>-2.6057</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7639</v>
+        <v>-1.6508</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9825</v>
+        <v>-2.4144</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4989</v>
+        <v>-1.7805</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4836</v>
+        <v>-0.6338</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2651</v>
+        <v>-0.3573</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08309999999999999</v>
+        <v>-0.2635</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3482</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7174</v>
+        <v>-2.0571</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.582</v>
+        <v>-1.517</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1354</v>
+        <v>-0.5401</v>
       </c>
       <c r="P21" t="n">
         <v>-1.5627</v>
@@ -2092,28 +2092,28 @@
         <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0336</v>
+        <v>-0.1685</v>
       </c>
       <c r="T21" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.295</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.049</v>
+        <v>0.1265</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1109</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3881</v>
+        <v>-0.1109</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6273</v>
+        <v>-4.8363</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7068</v>
+        <v>-3.2631</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9205</v>
+        <v>-1.5732</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4144</v>
+        <v>-2.9825</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7805</v>
+        <v>-1.4989</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6338</v>
+        <v>-1.4836</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3573</v>
+        <v>-1.2651</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2635</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-1.3482</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.0571</v>
+        <v>-1.7174</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.517</v>
+        <v>-1.582</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5401</v>
+        <v>-0.1354</v>
       </c>
       <c r="P22" t="n">
         <v>-1.5627</v>
@@ -2170,22 +2170,22 @@
         <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5393</v>
+        <v>-0.1802</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3961</v>
+        <v>-0.3218</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1432</v>
+        <v>0.1416</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1109</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1109</v>
+        <v>-0.3881</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2517</v>
+        <v>-4.995</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3018</v>
+        <v>-3.0996</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9499</v>
+        <v>-1.8955</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2369</v>
@@ -2248,13 +2248,13 @@
         <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4754</v>
+        <v>-0.2187</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2333</v>
+        <v>-0.1789</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-22.2591</v>
+        <v>-20.2367</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.7357</v>
+        <v>-9.735800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.5234</v>
+        <v>-10.5011</v>
       </c>
       <c r="G24" t="n">
         <v>-13.654</v>
@@ -2326,13 +2326,13 @@
         <v>11.7206</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.044599999999999</v>
+        <v>-2.0222</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.8467</v>
+        <v>-2.8466</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1979</v>
+        <v>0.8242999999999998</v>
       </c>
       <c r="V24" t="n">
         <v>5.2066</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484267_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484267_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-0.8865</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,48 +714,53 @@
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1447</v>
+        <v>3.2307</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4379</v>
+        <v>2.5239</v>
       </c>
       <c r="F4" t="n">
         <v>0.7068</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0083</v>
+        <v>1.0943</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9161</v>
+        <v>0.6091</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0922</v>
+        <v>0.4852</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1627</v>
+        <v>1.2487</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4748</v>
+        <v>1.1678</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6879</v>
+        <v>0.0809</v>
       </c>
       <c r="M4" t="n">
         <v>-0.1544</v>
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -792,7 +812,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -860,162 +880,177 @@
       </c>
       <c r="X5" t="n">
         <v>-2.1052</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4616</v>
+        <v>2.2689</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4326</v>
+        <v>1.633</v>
       </c>
       <c r="F6" t="n">
-        <v>1.029</v>
+        <v>0.6358</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7831</v>
+        <v>2.7479</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0668</v>
+        <v>1.4794</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2837</v>
+        <v>1.2685</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0912</v>
+        <v>1.6047</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9698</v>
+        <v>0.4707</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1214</v>
+        <v>1.134</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3081</v>
+        <v>1.1431</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.903</v>
+        <v>1.0087</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4051</v>
+        <v>0.1344</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1488</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5613</v>
+        <v>0.2001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3729</v>
+        <v>0.0283</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1883</v>
+        <v>0.1719</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0549</v>
+        <v>-2.4373</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2689</v>
+        <v>1.8476</v>
       </c>
       <c r="E7" t="n">
-        <v>1.633</v>
+        <v>0.8186</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6358</v>
+        <v>1.029</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7479</v>
+        <v>0.1691</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4794</v>
+        <v>0.4528</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2685</v>
+        <v>-0.2837</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6047</v>
+        <v>1.4772</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4707</v>
+        <v>1.3558</v>
       </c>
       <c r="L7" t="n">
-        <v>1.134</v>
+        <v>0.1214</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1431</v>
+        <v>-1.3081</v>
       </c>
       <c r="N7" t="n">
-        <v>1.0087</v>
+        <v>-0.903</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1344</v>
+        <v>-0.4051</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2001</v>
+        <v>0.5613</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0283</v>
+        <v>0.3729</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1719</v>
+        <v>0.1883</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.4373</v>
+        <v>-0.0549</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1026,143 +1061,148 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8761</v>
+        <v>0.914</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3314</v>
+        <v>0.914</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2075</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0045</v>
+        <v>0.914</v>
       </c>
       <c r="H8" t="n">
-        <v>0.614</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6184</v>
+        <v>0.607</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5688</v>
+        <v>0.914</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1077</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5389</v>
+        <v>0.607</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4937</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0795</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.595</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5185</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3903</v>
+        <v>0.914</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0153</v>
+        <v>0.914</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4056</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7832</v>
+        <v>0.914</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8371</v>
+        <v>0.307</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0539</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7793</v>
+        <v>0.914</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3725</v>
+        <v>0.307</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0039</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4646</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5393</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0255</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1356</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.161</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,162 +1212,177 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9814000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="E10" t="n">
-        <v>2.356</v>
+        <v>0.614</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3374</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.391</v>
+        <v>0.614</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4856</v>
+        <v>0.614</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0946</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0052</v>
+        <v>0.614</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9647</v>
+        <v>0.614</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6142</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4792</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.135</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3068</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3508</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.044</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.6559</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.6559</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3801</v>
+        <v>0.3903</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5327</v>
+        <v>-2.0153</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1526</v>
+        <v>2.4056</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5685</v>
+        <v>1.7832</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0373</v>
+        <v>1.8371</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6058</v>
+        <v>-0.0539</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0229</v>
+        <v>0.7793</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2827</v>
+        <v>1.3725</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7402</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4545</v>
+        <v>1.0039</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3201</v>
+        <v>0.4646</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1344</v>
+        <v>0.5393</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0303</v>
+        <v>-0.0255</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2475</v>
+        <v>0.1356</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2173</v>
+        <v>-0.161</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1338,470 +1393,496 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2955</v>
+        <v>0.307</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9558</v>
+        <v>0.307</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3397</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1753</v>
+        <v>0.307</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9233</v>
+        <v>0.307</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2521</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.2262</v>
+        <v>0.307</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9184</v>
+        <v>0.307</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3077</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9492</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0049</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9443</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3171</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2704</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0467</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.8643</v>
+        <v>-0.0379</v>
       </c>
       <c r="E13" t="n">
-        <v>13.1286</v>
+        <v>-1.2454</v>
       </c>
       <c r="F13" t="n">
-        <v>9.7356</v>
+        <v>1.2075</v>
       </c>
       <c r="G13" t="n">
-        <v>13.6539</v>
+        <v>-1.9184</v>
       </c>
       <c r="H13" t="n">
-        <v>14.3261</v>
+        <v>0.307</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6722000000000001</v>
+        <v>-2.2254</v>
       </c>
       <c r="J13" t="n">
-        <v>16.176</v>
+        <v>-0.3452</v>
       </c>
       <c r="K13" t="n">
-        <v>14.8209</v>
+        <v>0.8007</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3551</v>
+        <v>-1.1459</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5222</v>
+        <v>-1.5733</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4948000000000003</v>
+        <v>-0.4937</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.0272</v>
+        <v>-1.0795</v>
       </c>
       <c r="P13" t="n">
-        <v>9.767199999999999</v>
+        <v>1.5627</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.7204</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>21.4878</v>
+        <v>2.5395</v>
       </c>
       <c r="S13" t="n">
-        <v>4.6496</v>
+        <v>0.595</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8032</v>
+        <v>0.0765</v>
       </c>
       <c r="U13" t="n">
-        <v>2.846699999999999</v>
+        <v>0.5185</v>
       </c>
       <c r="V13" t="n">
-        <v>-5.2066</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8699</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-12.0765</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2146</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6571</v>
+        <v>2.356</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5574</v>
+        <v>-3.3374</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.1933</v>
+        <v>1.391</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.085</v>
+        <v>1.4856</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1084</v>
+        <v>-0.0946</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5506</v>
+        <v>2.0052</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7125</v>
+        <v>1.9647</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1619</v>
+        <v>0.0405</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.6427</v>
+        <v>-0.6142</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3725</v>
+        <v>-0.4792</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2702</v>
+        <v>-0.135</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4079</v>
+        <v>0.3068</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1026</v>
+        <v>0.3508</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3053</v>
+        <v>-0.044</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4373</v>
+        <v>-3.6559</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1052</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3321</v>
+        <v>-3.6559</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4174</v>
+        <v>-2.3801</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4025</v>
+        <v>-4.5327</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9851</v>
+        <v>2.1526</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0398</v>
+        <v>-0.5685</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8754</v>
+        <v>0.0373</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8356</v>
+        <v>-0.6058</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5015</v>
+        <v>-1.0229</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1256</v>
+        <v>-0.2827</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3758</v>
+        <v>-0.7402</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5413</v>
+        <v>0.4545</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.001</v>
+        <v>0.3201</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5403</v>
+        <v>0.1344</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2421</v>
+        <v>-0.0303</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0989</v>
+        <v>-0.2475</v>
       </c>
       <c r="U15" t="n">
-        <v>0.341</v>
+        <v>0.2173</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1522</v>
+        <v>-0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1522</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>M. LLUCIA MONSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0392</v>
+        <v>-3.6025</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9702</v>
+        <v>-2.2628</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.931</v>
+        <v>-1.3397</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.9324</v>
+        <v>-3.4823</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.7859</v>
+        <v>-1.2303</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1465</v>
+        <v>-2.2521</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.2561</v>
+        <v>-2.5331</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6501</v>
+        <v>-1.2254</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.606</v>
+        <v>-1.3077</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.6763</v>
+        <v>-0.9492</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.1358</v>
+        <v>-0.0049</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5405</v>
+        <v>-0.9443</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2373</v>
+        <v>0.3171</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3747</v>
+        <v>0.2704</v>
       </c>
       <c r="U16" t="n">
-        <v>0.612</v>
+        <v>0.0467</v>
       </c>
       <c r="V16" t="n">
-        <v>2.7809</v>
+        <v>-1.2186</v>
       </c>
       <c r="W16" t="n">
-        <v>3.601</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4747</v>
+        <v>22.8643</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3348</v>
+        <v>13.1286</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1399</v>
+        <v>9.735599999999998</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1225</v>
+        <v>13.654</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3878</v>
+        <v>14.3261</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5103</v>
+        <v>-0.6721999999999997</v>
       </c>
       <c r="J17" t="n">
-        <v>1.766</v>
+        <v>16.1761</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0642</v>
+        <v>14.8209</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7017</v>
+        <v>1.3551</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6435</v>
+        <v>-2.5222</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.452</v>
+        <v>-0.4948000000000003</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8085</v>
+        <v>-2.0272</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1721</v>
+        <v>9.767199999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-11.7204</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>21.4878</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4251</v>
+        <v>4.6496</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3892</v>
+        <v>1.8032</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0359</v>
+        <v>2.846699999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-5.2066</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>6.8699</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-12.0765</v>
+      </c>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.872</v>
+        <v>2.2146</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6709000000000001</v>
+        <v>1.6571</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2011</v>
+        <v>0.5574</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5086000000000001</v>
+        <v>-2.1933</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7168</v>
+        <v>-2.085</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2254</v>
+        <v>-0.1084</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2313</v>
+        <v>-0.5506</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2648</v>
+        <v>-0.7125</v>
       </c>
       <c r="L18" t="n">
-        <v>2.496</v>
+        <v>0.1619</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7226</v>
+        <v>-1.6427</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.452</v>
+        <v>-1.3725</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2706</v>
+        <v>-0.2702</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.7348</v>
+        <v>1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.8836</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6871</v>
+        <v>0.4079</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4559</v>
+        <v>0.1026</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2312</v>
+        <v>0.3053</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0413</v>
+        <v>2.4373</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4373</v>
+        <v>2.1052</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3959</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5246</v>
+        <v>0.4174</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6051</v>
+        <v>2.4025</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9195</v>
+        <v>-1.9851</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0545</v>
+        <v>-0.0398</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5024</v>
+        <v>-0.8754</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5521</v>
+        <v>0.8356</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7821</v>
+        <v>2.5015</v>
       </c>
       <c r="K19" t="n">
-        <v>3.0941</v>
+        <v>1.1256</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6879</v>
+        <v>1.3758</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7275</v>
+        <v>-2.5413</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5917</v>
+        <v>-2.001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1358</v>
+        <v>-0.5403</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.4929</v>
+        <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.8603</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5847</v>
+        <v>0.2421</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.0989</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1608</v>
+        <v>0.341</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4984</v>
+        <v>-1.1522</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7202</v>
+        <v>-1.1522</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BALLO RODRIGUEZ</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9488</v>
+        <v>0.0392</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.1864</v>
+        <v>0.9702</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7624</v>
+        <v>-0.931</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5403</v>
+        <v>-4.9324</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2704</v>
+        <v>-3.7859</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2698</v>
+        <v>-1.1465</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9814</v>
+        <v>-2.2561</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3073</v>
+        <v>-1.6501</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6741</v>
+        <v>-0.606</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5589</v>
+        <v>-2.6763</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-2.1358</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4043</v>
+        <v>-0.5405</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6452</v>
+        <v>0.2373</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2283</v>
+        <v>-0.3747</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4169</v>
+        <v>0.612</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1773</v>
+        <v>2.7809</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.601</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1773</v>
+        <v>-0.8201000000000001</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2565</v>
+        <v>-0.4747</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6057</v>
+        <v>-0.3348</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6508</v>
+        <v>-0.1399</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4144</v>
+        <v>1.1225</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7805</v>
+        <v>-0.3878</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6338</v>
+        <v>1.5103</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3573</v>
+        <v>1.766</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2635</v>
+        <v>1.0642</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.7017</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0571</v>
+        <v>-0.6435</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.517</v>
+        <v>-1.452</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5401</v>
+        <v>0.8085</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1685</v>
+        <v>-0.4251</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.295</v>
+        <v>-0.3892</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1265</v>
+        <v>-0.0359</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1109</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1109</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8363</v>
+        <v>-1.872</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2631</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5732</v>
+        <v>-1.2011</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9825</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4989</v>
+        <v>-1.7168</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4836</v>
+        <v>2.2254</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2651</v>
+        <v>2.2313</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08309999999999999</v>
+        <v>-0.2648</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3482</v>
+        <v>2.496</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7174</v>
+        <v>-1.7226</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.582</v>
+        <v>-1.452</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1354</v>
+        <v>-0.2706</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5627</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>-4.8836</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1802</v>
+        <v>-0.6871</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3218</v>
+        <v>-0.4559</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1416</v>
+        <v>-0.2312</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1109</v>
+        <v>1.0413</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2772</v>
+        <v>2.4373</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3881</v>
+        <v>-1.3959</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.995</v>
+        <v>-2.5246</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0996</v>
+        <v>-1.6051</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8955</v>
+        <v>-0.9195</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2369</v>
+        <v>2.0545</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4277</v>
+        <v>1.5024</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8091</v>
+        <v>0.5521</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3482</v>
+        <v>3.7821</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6741</v>
+        <v>3.0941</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6741</v>
+        <v>0.6879</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8887</v>
+        <v>-1.7275</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7536</v>
+        <v>-1.5917</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.135</v>
+        <v>-0.1358</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.5395</v>
+        <v>-4.4929</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>-5.8603</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3907</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2187</v>
+        <v>-0.5847</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0399</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1789</v>
+        <v>0.1608</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.4984</v>
       </c>
       <c r="W23" t="n">
         <v>1.2186</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>-0.7202</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>D. BALLO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,401 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
+        <v>-3.9488</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.1864</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-0.7624</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.5403</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.2704</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.2698</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.9814</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-1.3073</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.5589</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.9631999999999999</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.6452</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.2283</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.4169</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.1773</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.1773</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>J. CALLAVE FERRER</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.2565</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.6057</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.6508</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.4144</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.7805</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.6338</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.3573</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.2635</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.09379999999999999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.0571</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.517</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.5401</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.1685</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.295</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.1109</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.1109</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M. MONTSERRAT SERRA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.8363</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.2631</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-1.5732</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2.9825</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.4989</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.4836</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.2651</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.08309999999999999</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.3482</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.7174</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.582</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.1354</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.1802</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.3218</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.1109</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.3881</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A. CANO CANO</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.995</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.0996</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.8955</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.2369</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.4277</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.8091</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.3482</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.6741</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.8887</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.7536</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.135</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-2.5395</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.2187</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.0399</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1789</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484267_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>-20.2367</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E28" t="n">
         <v>-9.735800000000001</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F28" t="n">
         <v>-10.5011</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G28" t="n">
         <v>-13.654</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H28" t="n">
         <v>-14.326</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I28" t="n">
         <v>0.6722</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J28" t="n">
         <v>2.5222</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K28" t="n">
         <v>0.4947</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L28" t="n">
         <v>2.0271</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M28" t="n">
         <v>-16.176</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N28" t="n">
         <v>-14.8208</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O28" t="n">
         <v>-1.3551</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P28" t="n">
         <v>-9.767200000000001</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q28" t="n">
         <v>-21.4876</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R28" t="n">
         <v>11.7206</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S28" t="n">
         <v>-2.0222</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T28" t="n">
         <v>-2.8466</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U28" t="n">
         <v>0.8242999999999998</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V28" t="n">
         <v>5.2066</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W28" t="n">
         <v>12.0765</v>
       </c>
-      <c r="X24" t="n">
+      <c r="X28" t="n">
         <v>-6.8698</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
